--- a/results/Int All Data -0.0/Rando_4_permute.xlsx
+++ b/results/Int All Data -0.0/Rando_4_permute.xlsx
@@ -440,847 +440,847 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9671535239551019</v>
+        <v>0.9878782088747022</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9674850889418394</v>
+        <v>0.9878782088747022</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9685013262599469</v>
+        <v>0.9893768076848146</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9685013262599469</v>
+        <v>0.9897083726715521</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9694744788622638</v>
+        <v>0.9897299150294474</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.965495699021415</v>
+        <v>0.9897299150294474</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9664903939816272</v>
+        <v>0.9897299150294474</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9664903939816272</v>
+        <v>0.990126107089871</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9701376088357385</v>
+        <v>0.9891314121296588</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9840633382787094</v>
+        <v>0.9898376268189243</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9840633382787094</v>
+        <v>0.9895060618321869</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9834002083052347</v>
+        <v>0.9855272819913381</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9757742136102744</v>
+        <v>0.9851957170046006</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9757742136102744</v>
+        <v>0.9905007567923991</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9756665018207975</v>
+        <v>0.9928217116995609</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9690136597281542</v>
+        <v>0.9928217116995609</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9686605523835214</v>
+        <v>0.9935494687467218</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9713561569932114</v>
+        <v>0.9928863387732469</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.970714569377632</v>
+        <v>0.9868619715565946</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9674420042260486</v>
+        <v>0.9868619715565946</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9651210493188869</v>
+        <v>0.9850748924755354</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9651210493188869</v>
+        <v>0.9850748924755354</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9657626369344663</v>
+        <v>0.9823792878658454</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.9670027274498345</v>
+        <v>0.9833524404681623</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9679974224100467</v>
+        <v>0.9794898020350972</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9673342924365718</v>
+        <v>0.9788266720616223</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.9710030496485786</v>
+        <v>0.9776811805961426</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.9703614620329992</v>
+        <v>0.9787405026300409</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.9639755578534071</v>
+        <v>0.9787405026300409</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.9650779646030961</v>
+        <v>0.9784089376433035</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.966425766907941</v>
+        <v>0.9780342879407754</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.980661518979754</v>
+        <v>0.9795544291087832</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.980661518979754</v>
+        <v>0.9795544291087832</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.9816131292241754</v>
+        <v>0.9837701748864811</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.9850364908810263</v>
+        <v>0.983085502555111</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.9843733609075515</v>
+        <v>0.9841448245890092</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.9843733609075515</v>
+        <v>0.9841448245890092</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.9822547168397548</v>
+        <v>0.9827108528525828</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.9819446942109128</v>
+        <v>0.9840586551574277</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.9836456038603906</v>
+        <v>0.9868619715565946</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.9837102309340766</v>
+        <v>0.9903284179292362</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.9840202535629187</v>
+        <v>0.9892906382532332</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.9482112349952794</v>
+        <v>0.9899322258688127</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.9482112349952794</v>
+        <v>0.9899322258688127</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.9392589803533695</v>
+        <v>0.9895791185241799</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.9329807879632543</v>
+        <v>0.9843387058100677</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.9369380254462079</v>
+        <v>0.9724454510033118</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.9394612911927348</v>
+        <v>0.9724454510033118</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.9411622008422125</v>
+        <v>0.9723808239296258</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.9421999805182155</v>
+        <v>0.9706283999460504</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.9387335341455739</v>
+        <v>0.9682859026809932</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.9313098502899788</v>
+        <v>0.97638114612837</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.9332776978525079</v>
+        <v>0.9734616883214195</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.9285927033223935</v>
+        <v>0.9808207451033284</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.9285711609644982</v>
+        <v>0.9820392932608012</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.9144000359663715</v>
+        <v>0.9813330785715356</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8962501311273958</v>
+        <v>0.9820392932608012</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8956085435118164</v>
+        <v>0.9767127111151074</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8989672780949811</v>
+        <v>0.9720061742270977</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8907643228581277</v>
+        <v>0.9656633547632963</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8957377976591887</v>
+        <v>0.9618222586881267</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8658754064949272</v>
+        <v>0.9625284733773922</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8663146832711415</v>
+        <v>0.9631700609929716</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8566992986557569</v>
+        <v>0.965331789776559</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.8570308636424943</v>
+        <v>0.9639493323742301</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.8410511172054129</v>
+        <v>0.9634454285243297</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.8476824169401609</v>
+        <v>0.9664295134049663</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.8463561569932114</v>
+        <v>0.9653701913710681</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.8456283999460504</v>
+        <v>0.9654348184447541</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.8224188508744323</v>
+        <v>0.9544285468087339</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.824373585697373</v>
+        <v>0.9574772587630566</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.8240204783527403</v>
+        <v>0.959466648683481</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8212602466693641</v>
+        <v>0.9442362016514559</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8310779421241139</v>
+        <v>0.9384488003716525</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7729894423713828</v>
+        <v>0.9384272580137571</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7729894423713828</v>
+        <v>0.9384272580137571</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7719947474111706</v>
+        <v>0.9362355572539676</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.7768820527806501</v>
+        <v>0.9295827151613241</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.776481177598945</v>
+        <v>0.9274640710935276</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.7616853242218526</v>
+        <v>0.9440207780725023</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.7616853242218526</v>
+        <v>0.9443176879617557</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.7597390190172189</v>
+        <v>0.9427544620779571</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.7475994320310511</v>
+        <v>0.9415574562783797</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.7680571790375998</v>
+        <v>0.9398996313446928</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.7540836817575567</v>
+        <v>0.8943356711474771</v>
       </c>
     </row>
     <row r="87">
@@ -1290,663 +1290,663 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.7306980473257504</v>
+        <v>0.8901414677276747</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7714674279548622</v>
+        <v>0.8926132191401039</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.7744384000959104</v>
+        <v>0.8595719252498913</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.7507802080055148</v>
+        <v>0.8595719252498913</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.7471545355092988</v>
+        <v>0.8571086034557689</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.7137301622982511</v>
+        <v>0.8592703322393562</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.7160342579687992</v>
+        <v>0.8315125357790466</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.7166758455843787</v>
+        <v>0.8303885866714622</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.7243055867763641</v>
+        <v>0.8304747561030437</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.727392700325196</v>
+        <v>0.8224310269897646</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.6749155164920799</v>
+        <v>0.8156142756522651</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.6985334337394536</v>
+        <v>0.7384514229195702</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6742074285543018</v>
+        <v>0.7416031635420881</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.6799002307842168</v>
+        <v>0.7147670053499977</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.6350509148945735</v>
+        <v>0.7144138980053649</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5317094141977251</v>
+        <v>0.7042899264187984</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5171505267574817</v>
+        <v>0.7099181015750273</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5036902995699022</v>
+        <v>0.7028774970402674</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5036902995699022</v>
+        <v>0.7050176834659594</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.4894320685159376</v>
+        <v>0.7067185931154371</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.4901382832052031</v>
+        <v>0.7070717004600698</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.4901382832052031</v>
+        <v>0.7267295703517211</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.4901382832052031</v>
+        <v>0.7238747396184567</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5042494642509254</v>
+        <v>0.7242278469630895</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5120178258328463</v>
+        <v>0.7233277510527657</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.512636934466274</v>
+        <v>0.6600437965502255</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5140025326319891</v>
+        <v>0.6671059434428809</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5113500127380899</v>
+        <v>0.6727556609570051</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.51203468506946</v>
+        <v>0.6706585592471039</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5009328777592951</v>
+        <v>0.6797962654917652</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.4735497310015136</v>
+        <v>0.6681437231188838</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.4735497310015136</v>
+        <v>0.6681437231188838</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.4731451093227832</v>
+        <v>0.6398520508324717</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.4802456578099477</v>
+        <v>0.6091317118494208</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4935682012318482</v>
+        <v>0.6116034632618501</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4886631000014986</v>
+        <v>0.6116034632618501</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4858382412444364</v>
+        <v>0.6126627852957485</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4501069624900718</v>
+        <v>0.6126627852957485</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4504600698347045</v>
+        <v>0.6126627852957485</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.426471249381828</v>
+        <v>0.6130158926403813</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4375243522306643</v>
+        <v>0.5949858757062148</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4360903804942379</v>
+        <v>0.6010102429228671</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4789006653778717</v>
+        <v>0.5915409716914685</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4779059704176595</v>
+        <v>0.5664272655067513</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4714554391643813</v>
+        <v>0.5756295988250986</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4707492244751157</v>
+        <v>0.5759611638118359</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4707492244751157</v>
+        <v>0.55545939546524</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4691560266151149</v>
+        <v>0.5512436496875421</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.475369591931544</v>
+        <v>0.5512436496875421</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.4611122975018358</v>
+        <v>0.5509120847008048</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4604276251704656</v>
+        <v>0.5604459830058894</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4709946200302716</v>
+        <v>0.5434537457477259</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4897861124848267</v>
+        <v>0.5434537457477259</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.4897861124848267</v>
+        <v>0.5491250056197455</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4897861124848267</v>
+        <v>0.5095985253787708</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.4937648923256755</v>
+        <v>0.5095985253787708</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.4967274348484167</v>
+        <v>0.5187577739813275</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.4973905648218915</v>
+        <v>0.5325505027799008</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.4970805421930495</v>
+        <v>0.5328820677666382</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.4970805421930495</v>
+        <v>0.5162429378531074</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.4970805421930495</v>
+        <v>0.5162429378531074</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4986737400530504</v>
+        <v>0.5060243672166524</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4986737400530504</v>
+        <v>0.5052966101694916</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.5000215423578953</v>
+        <v>0.5052966101694916</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.5000215423578953</v>
+        <v>0.5056497175141242</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.5000215423578953</v>
+        <v>0.5039272655067512</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -1956,31 +1956,31 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.5007277570471609</v>
+        <v>0.5003746497025281</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.5007277570471609</v>
+        <v>0.5011670338233751</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.5007277570471609</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
